--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452235047349248</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39656923</v>
+        <v>3967972</v>
       </c>
       <c r="L2" t="n">
-        <v>21771413</v>
+        <v>1867200</v>
       </c>
       <c r="M2" t="n">
-        <v>5045250</v>
+        <v>394199</v>
       </c>
       <c r="N2" t="n">
-        <v>206171</v>
+        <v>11301</v>
       </c>
       <c r="O2" t="n">
-        <v>2937265</v>
+        <v>224465</v>
       </c>
       <c r="P2" t="n">
-        <v>1193907</v>
+        <v>97010</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998995065689087</v>
+        <v>0.9999111294746399</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8591343760490417</v>
+        <v>0.7624653577804565</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7323987483978271</v>
+        <v>0.5735693573951721</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6643828153610229</v>
+        <v>0.4627150595188141</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1905488520860672</v>
+        <v>0.08804281800985336</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7162546515464783</v>
+        <v>0.52836674451828</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8057096600532532</v>
+        <v>0.6407064199447632</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026323576521127</v>
       </c>
       <c r="C3" t="n">
-        <v>1852</v>
+        <v>217</v>
       </c>
       <c r="D3" t="n">
-        <v>39656923</v>
+        <v>3967972</v>
       </c>
       <c r="E3" t="n">
-        <v>5291090</v>
+        <v>957322</v>
       </c>
       <c r="F3" t="n">
-        <v>142779</v>
+        <v>43245</v>
       </c>
       <c r="G3" t="n">
-        <v>13349</v>
+        <v>3598</v>
       </c>
       <c r="H3" t="n">
-        <v>8959</v>
+        <v>3007</v>
       </c>
       <c r="I3" t="n">
-        <v>676</v>
+        <v>294</v>
       </c>
       <c r="J3" t="n">
-        <v>90143887</v>
+        <v>10016061</v>
       </c>
       <c r="K3" t="n">
-        <v>95348533</v>
+        <v>10117783</v>
       </c>
       <c r="L3" t="n">
-        <v>109521450</v>
+        <v>11635072</v>
       </c>
       <c r="M3" t="n">
-        <v>136007063</v>
+        <v>14931994</v>
       </c>
       <c r="N3" t="n">
-        <v>145286830</v>
+        <v>16122846</v>
       </c>
       <c r="O3" t="n">
-        <v>141214277</v>
+        <v>15617856</v>
       </c>
       <c r="P3" t="n">
-        <v>144937691</v>
+        <v>16081513</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8790063261985779</v>
+        <v>0.7974773049354553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7382595539093018</v>
+        <v>0.5647359490394592</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5998610854148865</v>
+        <v>0.4194146394729614</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2565094530582428</v>
+        <v>0.1259908378124237</v>
       </c>
       <c r="V3" t="n">
-        <v>0.640133261680603</v>
+        <v>0.4389388859272003</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6858349442481995</v>
+        <v>0.5008622407913208</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03197108341586186</v>
       </c>
       <c r="C4" t="n">
-        <v>238</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>6060477</v>
+        <v>1132851</v>
       </c>
       <c r="E4" t="n">
-        <v>21771413</v>
+        <v>1867200</v>
       </c>
       <c r="F4" t="n">
-        <v>1422019</v>
+        <v>246093</v>
       </c>
       <c r="G4" t="n">
-        <v>86558</v>
+        <v>20710</v>
       </c>
       <c r="H4" t="n">
-        <v>133850</v>
+        <v>34519</v>
       </c>
       <c r="I4" t="n">
-        <v>15633</v>
+        <v>4909</v>
       </c>
       <c r="J4" t="n">
-        <v>5711</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>6502239</v>
+        <v>1236162</v>
       </c>
       <c r="L4" t="n">
-        <v>7954762</v>
+        <v>1388204</v>
       </c>
       <c r="M4" t="n">
-        <v>2548640</v>
+        <v>457727</v>
       </c>
       <c r="N4" t="n">
-        <v>875814</v>
+        <v>117057</v>
       </c>
       <c r="O4" t="n">
-        <v>1163602</v>
+        <v>200363</v>
       </c>
       <c r="P4" t="n">
-        <v>287901</v>
+        <v>54401</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999497532844543</v>
+        <v>0.9999555945396423</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8689567446708679</v>
+        <v>0.7795783877372742</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7353174686431885</v>
+        <v>0.5691183805465698</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6304755210876465</v>
+        <v>0.4400021433830261</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2186631113290787</v>
+        <v>0.1036527454853058</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6760579943656921</v>
+        <v>0.4795189499855042</v>
       </c>
       <c r="W4" t="n">
-        <v>0.740955114364624</v>
+        <v>0.5622187256813049</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1734</v>
+        <v>194</v>
       </c>
       <c r="D5" t="n">
-        <v>305344</v>
+        <v>76199</v>
       </c>
       <c r="E5" t="n">
-        <v>2208885</v>
+        <v>334352</v>
       </c>
       <c r="F5" t="n">
-        <v>5045250</v>
+        <v>394199</v>
       </c>
       <c r="G5" t="n">
-        <v>299853</v>
+        <v>35910</v>
       </c>
       <c r="H5" t="n">
-        <v>492025</v>
+        <v>85036</v>
       </c>
       <c r="I5" t="n">
-        <v>57606</v>
+        <v>13989</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5458705</v>
+        <v>1007683</v>
       </c>
       <c r="L5" t="n">
-        <v>7718775</v>
+        <v>1439124</v>
       </c>
       <c r="M5" t="n">
-        <v>3365447</v>
+        <v>545680</v>
       </c>
       <c r="N5" t="n">
-        <v>597585</v>
+        <v>78396</v>
       </c>
       <c r="O5" t="n">
-        <v>1651256</v>
+        <v>286916</v>
       </c>
       <c r="P5" t="n">
-        <v>546901</v>
+        <v>96676</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999611377716064</v>
+        <v>0.9999656677246094</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9186144471168518</v>
+        <v>0.8625903129577637</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8933529257774353</v>
+        <v>0.8268586993217468</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9597589373588562</v>
+        <v>0.9385528564453125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9899745583534241</v>
+        <v>0.988030731678009</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9808469414710999</v>
+        <v>0.9701597690582275</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9943197965621948</v>
+        <v>0.9907482862472534</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>117402</v>
+        <v>18479</v>
       </c>
       <c r="E6" t="n">
-        <v>190547</v>
+        <v>24063</v>
       </c>
       <c r="F6" t="n">
-        <v>197659</v>
+        <v>24361</v>
       </c>
       <c r="G6" t="n">
-        <v>206171</v>
+        <v>11301</v>
       </c>
       <c r="H6" t="n">
-        <v>83374</v>
+        <v>9827</v>
       </c>
       <c r="I6" t="n">
-        <v>8299</v>
+        <v>1640</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>339</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>18362</v>
+        <v>8369</v>
       </c>
       <c r="E7" t="n">
-        <v>243410</v>
+        <v>65214</v>
       </c>
       <c r="F7" t="n">
-        <v>737120</v>
+        <v>129935</v>
       </c>
       <c r="G7" t="n">
-        <v>446338</v>
+        <v>49799</v>
       </c>
       <c r="H7" t="n">
-        <v>2937265</v>
+        <v>224465</v>
       </c>
       <c r="I7" t="n">
-        <v>205687</v>
+        <v>33569</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1244</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>654</v>
+        <v>264</v>
       </c>
       <c r="E8" t="n">
-        <v>20830</v>
+        <v>7253</v>
       </c>
       <c r="F8" t="n">
-        <v>49063</v>
+        <v>14093</v>
       </c>
       <c r="G8" t="n">
-        <v>29716</v>
+        <v>7040</v>
       </c>
       <c r="H8" t="n">
-        <v>445394</v>
+        <v>67974</v>
       </c>
       <c r="I8" t="n">
-        <v>1193907</v>
+        <v>97010</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
